--- a/examples/qualibact_ecoli/real_run_100/report/report.xlsx
+++ b/examples/qualibact_ecoli/real_run_100/report/report.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12137,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12848,7 +12848,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13006,7 +13006,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13243,7 +13243,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13638,7 +13638,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13717,7 +13717,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14270,7 +14270,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14902,7 +14902,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -14981,7 +14981,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15613,7 +15613,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15771,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -16087,7 +16087,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -16245,7 +16245,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -16324,7 +16324,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
     </row>
@@ -17144,17 +17144,17 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -17502,17 +17502,17 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -17860,17 +17860,17 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -18218,17 +18218,17 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -18572,17 +18572,17 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
@@ -18626,7 +18626,7 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -18922,17 +18922,17 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
@@ -18976,7 +18976,7 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -19272,17 +19272,17 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
@@ -19326,7 +19326,7 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -19626,17 +19626,17 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -19984,17 +19984,17 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -20342,17 +20342,17 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -20700,17 +20700,17 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
@@ -20758,7 +20758,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -21058,17 +21058,17 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX13" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -21416,17 +21416,17 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX14" t="inlineStr">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -21774,17 +21774,17 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX15" t="inlineStr">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -22132,17 +22132,17 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX16" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -22490,17 +22490,17 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX17" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -22848,17 +22848,17 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX18" t="inlineStr">
@@ -22906,7 +22906,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -23206,17 +23206,17 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX19" t="inlineStr">
@@ -23264,7 +23264,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -23564,17 +23564,17 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -23922,17 +23922,17 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX21" t="inlineStr">
@@ -23980,7 +23980,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -24280,17 +24280,17 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
@@ -24338,7 +24338,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -24638,17 +24638,17 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
@@ -24696,7 +24696,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -24996,17 +24996,17 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX24" t="inlineStr">
@@ -25054,7 +25054,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -25354,17 +25354,17 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX25" t="inlineStr">
@@ -25412,7 +25412,7 @@
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -25712,17 +25712,17 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX26" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -26070,17 +26070,17 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX27" t="inlineStr">
@@ -26128,7 +26128,7 @@
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -26428,17 +26428,17 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW28" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX28" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -26786,17 +26786,17 @@
       </c>
       <c r="BU29" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW29" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX29" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -27144,17 +27144,17 @@
       </c>
       <c r="BU30" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW30" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX30" t="inlineStr">
@@ -27202,7 +27202,7 @@
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -27502,17 +27502,17 @@
       </c>
       <c r="BU31" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV31" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW31" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX31" t="inlineStr">
@@ -27560,7 +27560,7 @@
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -27860,17 +27860,17 @@
       </c>
       <c r="BU32" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX32" t="inlineStr">
@@ -27918,7 +27918,7 @@
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -28218,17 +28218,17 @@
       </c>
       <c r="BU33" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX33" t="inlineStr">
@@ -28276,7 +28276,7 @@
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -28576,17 +28576,17 @@
       </c>
       <c r="BU34" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX34" t="inlineStr">
@@ -28634,7 +28634,7 @@
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">
@@ -28934,17 +28934,17 @@
       </c>
       <c r="BU35" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV35" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW35" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX35" t="inlineStr">
@@ -28992,7 +28992,7 @@
       </c>
       <c r="CG35" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH35" t="inlineStr">
@@ -29292,17 +29292,17 @@
       </c>
       <c r="BU36" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV36" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW36" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX36" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="CG36" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH36" t="inlineStr">
@@ -29650,17 +29650,17 @@
       </c>
       <c r="BU37" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV37" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW37" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX37" t="inlineStr">
@@ -29708,7 +29708,7 @@
       </c>
       <c r="CG37" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH37" t="inlineStr">
@@ -30008,17 +30008,17 @@
       </c>
       <c r="BU38" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV38" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW38" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX38" t="inlineStr">
@@ -30066,7 +30066,7 @@
       </c>
       <c r="CG38" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH38" t="inlineStr">
@@ -30366,17 +30366,17 @@
       </c>
       <c r="BU39" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV39" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW39" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX39" t="inlineStr">
@@ -30424,7 +30424,7 @@
       </c>
       <c r="CG39" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH39" t="inlineStr">
@@ -30724,17 +30724,17 @@
       </c>
       <c r="BU40" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV40" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW40" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX40" t="inlineStr">
@@ -30782,7 +30782,7 @@
       </c>
       <c r="CG40" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH40" t="inlineStr">
@@ -31082,17 +31082,17 @@
       </c>
       <c r="BU41" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV41" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW41" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX41" t="inlineStr">
@@ -31140,7 +31140,7 @@
       </c>
       <c r="CG41" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH41" t="inlineStr">
@@ -31440,17 +31440,17 @@
       </c>
       <c r="BU42" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV42" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW42" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX42" t="inlineStr">
@@ -31498,7 +31498,7 @@
       </c>
       <c r="CG42" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH42" t="inlineStr">
@@ -31798,17 +31798,17 @@
       </c>
       <c r="BU43" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV43" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW43" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX43" t="inlineStr">
@@ -31856,7 +31856,7 @@
       </c>
       <c r="CG43" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH43" t="inlineStr">
@@ -32156,17 +32156,17 @@
       </c>
       <c r="BU44" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV44" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW44" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX44" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="CG44" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH44" t="inlineStr">
@@ -32514,17 +32514,17 @@
       </c>
       <c r="BU45" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV45" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW45" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX45" t="inlineStr">
@@ -32572,7 +32572,7 @@
       </c>
       <c r="CG45" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH45" t="inlineStr">
@@ -32872,17 +32872,17 @@
       </c>
       <c r="BU46" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV46" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW46" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX46" t="inlineStr">
@@ -32930,7 +32930,7 @@
       </c>
       <c r="CG46" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH46" t="inlineStr">
@@ -33230,17 +33230,17 @@
       </c>
       <c r="BU47" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV47" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW47" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX47" t="inlineStr">
@@ -33288,7 +33288,7 @@
       </c>
       <c r="CG47" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH47" t="inlineStr">
@@ -33588,17 +33588,17 @@
       </c>
       <c r="BU48" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV48" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW48" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX48" t="inlineStr">
@@ -33646,7 +33646,7 @@
       </c>
       <c r="CG48" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH48" t="inlineStr">
@@ -33946,17 +33946,17 @@
       </c>
       <c r="BU49" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV49" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW49" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX49" t="inlineStr">
@@ -34004,7 +34004,7 @@
       </c>
       <c r="CG49" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH49" t="inlineStr">
@@ -34304,17 +34304,17 @@
       </c>
       <c r="BU50" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV50" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW50" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX50" t="inlineStr">
@@ -34362,7 +34362,7 @@
       </c>
       <c r="CG50" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH50" t="inlineStr">
@@ -34662,17 +34662,17 @@
       </c>
       <c r="BU51" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV51" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW51" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX51" t="inlineStr">
@@ -34720,7 +34720,7 @@
       </c>
       <c r="CG51" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH51" t="inlineStr">
@@ -35020,17 +35020,17 @@
       </c>
       <c r="BU52" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV52" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW52" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX52" t="inlineStr">
@@ -35078,7 +35078,7 @@
       </c>
       <c r="CG52" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH52" t="inlineStr">
@@ -35378,17 +35378,17 @@
       </c>
       <c r="BU53" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV53" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW53" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX53" t="inlineStr">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="CG53" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH53" t="inlineStr">
@@ -35736,17 +35736,17 @@
       </c>
       <c r="BU54" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV54" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW54" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX54" t="inlineStr">
@@ -35794,7 +35794,7 @@
       </c>
       <c r="CG54" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH54" t="inlineStr">
@@ -36094,17 +36094,17 @@
       </c>
       <c r="BU55" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV55" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW55" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX55" t="inlineStr">
@@ -36152,7 +36152,7 @@
       </c>
       <c r="CG55" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH55" t="inlineStr">
@@ -36452,17 +36452,17 @@
       </c>
       <c r="BU56" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV56" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW56" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX56" t="inlineStr">
@@ -36510,7 +36510,7 @@
       </c>
       <c r="CG56" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH56" t="inlineStr">
@@ -36810,17 +36810,17 @@
       </c>
       <c r="BU57" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV57" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW57" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX57" t="inlineStr">
@@ -36868,7 +36868,7 @@
       </c>
       <c r="CG57" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH57" t="inlineStr">
@@ -37168,17 +37168,17 @@
       </c>
       <c r="BU58" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV58" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW58" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX58" t="inlineStr">
@@ -37226,7 +37226,7 @@
       </c>
       <c r="CG58" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH58" t="inlineStr">
@@ -37526,17 +37526,17 @@
       </c>
       <c r="BU59" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV59" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW59" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX59" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="CG59" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH59" t="inlineStr">
@@ -37884,17 +37884,17 @@
       </c>
       <c r="BU60" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV60" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW60" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX60" t="inlineStr">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="CG60" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH60" t="inlineStr">
@@ -38242,17 +38242,17 @@
       </c>
       <c r="BU61" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV61" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW61" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX61" t="inlineStr">
@@ -38300,7 +38300,7 @@
       </c>
       <c r="CG61" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH61" t="inlineStr">
@@ -38600,17 +38600,17 @@
       </c>
       <c r="BU62" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV62" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW62" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX62" t="inlineStr">
@@ -38658,7 +38658,7 @@
       </c>
       <c r="CG62" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH62" t="inlineStr">
@@ -38958,17 +38958,17 @@
       </c>
       <c r="BU63" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV63" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW63" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX63" t="inlineStr">
@@ -39016,7 +39016,7 @@
       </c>
       <c r="CG63" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH63" t="inlineStr">
@@ -39316,17 +39316,17 @@
       </c>
       <c r="BU64" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV64" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW64" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX64" t="inlineStr">
@@ -39374,7 +39374,7 @@
       </c>
       <c r="CG64" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH64" t="inlineStr">
@@ -39674,17 +39674,17 @@
       </c>
       <c r="BU65" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV65" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW65" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX65" t="inlineStr">
@@ -39732,7 +39732,7 @@
       </c>
       <c r="CG65" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH65" t="inlineStr">
@@ -40032,17 +40032,17 @@
       </c>
       <c r="BU66" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV66" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW66" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX66" t="inlineStr">
@@ -40090,7 +40090,7 @@
       </c>
       <c r="CG66" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH66" t="inlineStr">
@@ -40390,17 +40390,17 @@
       </c>
       <c r="BU67" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV67" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW67" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX67" t="inlineStr">
@@ -40448,7 +40448,7 @@
       </c>
       <c r="CG67" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH67" t="inlineStr">
@@ -40748,17 +40748,17 @@
       </c>
       <c r="BU68" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV68" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW68" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX68" t="inlineStr">
@@ -40806,7 +40806,7 @@
       </c>
       <c r="CG68" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH68" t="inlineStr">
@@ -41106,17 +41106,17 @@
       </c>
       <c r="BU69" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV69" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW69" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX69" t="inlineStr">
@@ -41164,7 +41164,7 @@
       </c>
       <c r="CG69" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH69" t="inlineStr">
@@ -41464,17 +41464,17 @@
       </c>
       <c r="BU70" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV70" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW70" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX70" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="CG70" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH70" t="inlineStr">
@@ -41822,17 +41822,17 @@
       </c>
       <c r="BU71" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV71" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW71" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX71" t="inlineStr">
@@ -41880,7 +41880,7 @@
       </c>
       <c r="CG71" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH71" t="inlineStr">
@@ -42180,17 +42180,17 @@
       </c>
       <c r="BU72" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV72" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW72" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX72" t="inlineStr">
@@ -42238,7 +42238,7 @@
       </c>
       <c r="CG72" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH72" t="inlineStr">
@@ -42538,17 +42538,17 @@
       </c>
       <c r="BU73" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV73" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW73" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX73" t="inlineStr">
@@ -42596,7 +42596,7 @@
       </c>
       <c r="CG73" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH73" t="inlineStr">
@@ -42896,17 +42896,17 @@
       </c>
       <c r="BU74" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV74" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW74" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX74" t="inlineStr">
@@ -42954,7 +42954,7 @@
       </c>
       <c r="CG74" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH74" t="inlineStr">
@@ -43254,17 +43254,17 @@
       </c>
       <c r="BU75" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV75" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW75" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX75" t="inlineStr">
@@ -43312,7 +43312,7 @@
       </c>
       <c r="CG75" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH75" t="inlineStr">
@@ -43612,17 +43612,17 @@
       </c>
       <c r="BU76" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV76" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW76" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX76" t="inlineStr">
@@ -43670,7 +43670,7 @@
       </c>
       <c r="CG76" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH76" t="inlineStr">
@@ -43970,17 +43970,17 @@
       </c>
       <c r="BU77" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV77" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW77" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX77" t="inlineStr">
@@ -44028,7 +44028,7 @@
       </c>
       <c r="CG77" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH77" t="inlineStr">
@@ -44328,17 +44328,17 @@
       </c>
       <c r="BU78" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV78" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW78" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX78" t="inlineStr">
@@ -44386,7 +44386,7 @@
       </c>
       <c r="CG78" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH78" t="inlineStr">
@@ -44686,17 +44686,17 @@
       </c>
       <c r="BU79" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV79" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW79" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX79" t="inlineStr">
@@ -44744,7 +44744,7 @@
       </c>
       <c r="CG79" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH79" t="inlineStr">
@@ -45044,17 +45044,17 @@
       </c>
       <c r="BU80" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV80" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW80" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX80" t="inlineStr">
@@ -45102,7 +45102,7 @@
       </c>
       <c r="CG80" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH80" t="inlineStr">
@@ -45402,17 +45402,17 @@
       </c>
       <c r="BU81" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV81" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW81" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX81" t="inlineStr">
@@ -45460,7 +45460,7 @@
       </c>
       <c r="CG81" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH81" t="inlineStr">
@@ -45760,17 +45760,17 @@
       </c>
       <c r="BU82" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV82" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW82" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX82" t="inlineStr">
@@ -45818,7 +45818,7 @@
       </c>
       <c r="CG82" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH82" t="inlineStr">
@@ -46118,17 +46118,17 @@
       </c>
       <c r="BU83" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV83" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW83" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX83" t="inlineStr">
@@ -46176,7 +46176,7 @@
       </c>
       <c r="CG83" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH83" t="inlineStr">
@@ -46476,17 +46476,17 @@
       </c>
       <c r="BU84" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV84" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW84" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX84" t="inlineStr">
@@ -46534,7 +46534,7 @@
       </c>
       <c r="CG84" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH84" t="inlineStr">
@@ -46834,17 +46834,17 @@
       </c>
       <c r="BU85" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV85" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW85" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX85" t="inlineStr">
@@ -46892,7 +46892,7 @@
       </c>
       <c r="CG85" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH85" t="inlineStr">
@@ -47192,17 +47192,17 @@
       </c>
       <c r="BU86" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV86" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW86" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX86" t="inlineStr">
@@ -47250,7 +47250,7 @@
       </c>
       <c r="CG86" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH86" t="inlineStr">
@@ -47550,17 +47550,17 @@
       </c>
       <c r="BU87" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV87" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW87" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX87" t="inlineStr">
@@ -47608,7 +47608,7 @@
       </c>
       <c r="CG87" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH87" t="inlineStr">
@@ -47908,17 +47908,17 @@
       </c>
       <c r="BU88" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV88" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW88" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX88" t="inlineStr">
@@ -47966,7 +47966,7 @@
       </c>
       <c r="CG88" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH88" t="inlineStr">
@@ -48266,17 +48266,17 @@
       </c>
       <c r="BU89" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV89" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW89" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX89" t="inlineStr">
@@ -48324,7 +48324,7 @@
       </c>
       <c r="CG89" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH89" t="inlineStr">
@@ -48624,17 +48624,17 @@
       </c>
       <c r="BU90" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV90" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW90" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX90" t="inlineStr">
@@ -48682,7 +48682,7 @@
       </c>
       <c r="CG90" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH90" t="inlineStr">
@@ -48982,17 +48982,17 @@
       </c>
       <c r="BU91" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV91" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW91" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX91" t="inlineStr">
@@ -49040,7 +49040,7 @@
       </c>
       <c r="CG91" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH91" t="inlineStr">
@@ -49340,17 +49340,17 @@
       </c>
       <c r="BU92" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV92" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW92" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX92" t="inlineStr">
@@ -49398,7 +49398,7 @@
       </c>
       <c r="CG92" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH92" t="inlineStr">
@@ -49698,17 +49698,17 @@
       </c>
       <c r="BU93" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV93" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW93" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX93" t="inlineStr">
@@ -49756,7 +49756,7 @@
       </c>
       <c r="CG93" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH93" t="inlineStr">
@@ -50056,17 +50056,17 @@
       </c>
       <c r="BU94" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV94" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW94" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX94" t="inlineStr">
@@ -50114,7 +50114,7 @@
       </c>
       <c r="CG94" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH94" t="inlineStr">
@@ -50414,17 +50414,17 @@
       </c>
       <c r="BU95" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV95" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW95" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX95" t="inlineStr">
@@ -50472,7 +50472,7 @@
       </c>
       <c r="CG95" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH95" t="inlineStr">
@@ -50772,17 +50772,17 @@
       </c>
       <c r="BU96" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV96" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW96" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX96" t="inlineStr">
@@ -50830,7 +50830,7 @@
       </c>
       <c r="CG96" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH96" t="inlineStr">
@@ -51130,17 +51130,17 @@
       </c>
       <c r="BU97" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV97" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW97" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX97" t="inlineStr">
@@ -51188,7 +51188,7 @@
       </c>
       <c r="CG97" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH97" t="inlineStr">
@@ -51488,17 +51488,17 @@
       </c>
       <c r="BU98" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV98" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW98" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX98" t="inlineStr">
@@ -51546,7 +51546,7 @@
       </c>
       <c r="CG98" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH98" t="inlineStr">
@@ -51846,17 +51846,17 @@
       </c>
       <c r="BU99" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV99" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW99" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX99" t="inlineStr">
@@ -51904,7 +51904,7 @@
       </c>
       <c r="CG99" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH99" t="inlineStr">
@@ -52204,17 +52204,17 @@
       </c>
       <c r="BU100" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV100" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW100" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX100" t="inlineStr">
@@ -52262,7 +52262,7 @@
       </c>
       <c r="CG100" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH100" t="inlineStr">
@@ -52562,17 +52562,17 @@
       </c>
       <c r="BU101" t="inlineStr">
         <is>
-          <t>qualibact-v1.1</t>
+          <t>qualibact-v1.0</t>
         </is>
       </c>
       <c r="BV101" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="BW101" t="inlineStr">
         <is>
-          <t>1.2.2</t>
+          <t>1.3.0</t>
         </is>
       </c>
       <c r="BX101" t="inlineStr">
@@ -52620,7 +52620,7 @@
       </c>
       <c r="CG101" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia coli qualibact-v1.1</t>
+          <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
       <c r="CH101" t="inlineStr">

--- a/examples/qualibact_ecoli/real_run_100/report/report.xlsx
+++ b/examples/qualibact_ecoli/real_run_100/report/report.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; GC_Content &gt;50.88; Genome_Size &lt;4400000.0</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; GC_Content &gt;50.88; Genome_Size &lt;4400000.0</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; Genome_Size &lt;4400000.0</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>GC_Content &lt;50.25; Genome_Size &gt;5700000.0</t>
+          <t>GC_Content &lt;50.09; Genome_Size &gt;5700000.0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>GC_Content &gt;50.88</t>
+          <t>GC_Content &gt;51.13; Total_Coding_Sequences &lt;4200.0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; no_of_contigs &gt;670.0</t>
+          <t>N50 &lt;20000.0; no_of_contigs &gt;670.0; Contamination &gt;2.0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Completeness_Specific &lt;100.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>GC_Content &lt;50.25; Genome_Size &gt;5700000.0; Total_Coding_Sequences &gt;5800.0</t>
+          <t>GC_Content &lt;50.09; Contamination &gt;2.0; Genome_Size &gt;5700000.0; Total_Coding_Sequences &gt;5800.0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; GC_Content &gt;50.88; Genome_Size &lt;4400000.0</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; GC_Content &gt;50.88; Genome_Size &lt;4400000.0</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; Genome_Size &lt;4400000.0</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -9068,12 +9068,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>GC_Content &lt;50.25; Genome_Size &gt;5700000.0</t>
+          <t>GC_Content &lt;50.09; Genome_Size &gt;5700000.0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>GC_Content &gt;50.88</t>
+          <t>GC_Content &gt;51.13; Total_Coding_Sequences &lt;4200.0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; no_of_contigs &gt;670.0</t>
+          <t>N50 &lt;20000.0; no_of_contigs &gt;670.0; Contamination &gt;2.0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Completeness_Specific &lt;100.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>GC_Content &lt;50.25; Genome_Size &gt;5700000.0; Total_Coding_Sequences &gt;5800.0</t>
+          <t>GC_Content &lt;50.09; Contamination &gt;2.0; Genome_Size &gt;5700000.0; Total_Coding_Sequences &gt;5800.0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -16161,7 +16161,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -16418,7 +16418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH101"/>
+  <dimension ref="A1:CJ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16824,30 +16824,40 @@
       </c>
       <c r="CC1" t="inlineStr">
         <is>
+          <t>qualibact_compat_metrics_evaluated</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>qualibact_compat_metrics_missing</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
           <t>overall_qc</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>baseline_qc</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>species_confidence</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>threshold_source</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>reason_summary</t>
         </is>
@@ -17179,33 +17189,39 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD2" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC2" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -17537,33 +17553,39 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD3" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF3" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -17895,33 +17917,39 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD4" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF4" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -18253,33 +18281,39 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD5" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF5" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -18587,17 +18621,17 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; GC_Content &gt;50.88; Genome_Size &lt;4400000.0</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -18607,31 +18641,37 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="CD6" t="b">
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC6" t="n">
         <v>0</v>
       </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>NOT_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="CF6" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>Unidentified</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="inlineStr">
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>N50 &lt;20000.0; GC_Content &gt;50.88; Genome_Size &lt;4400000.0</t>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
     </row>
@@ -18937,17 +18977,17 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; GC_Content &gt;50.88; Genome_Size &lt;4400000.0</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -18957,31 +18997,37 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="CD7" t="b">
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC7" t="n">
         <v>0</v>
       </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>NOT_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="CF7" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>Unidentified</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr">
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
-        <is>
-          <t>N50 &lt;20000.0; GC_Content &gt;50.88; Genome_Size &lt;4400000.0</t>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
     </row>
@@ -19287,17 +19333,17 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; Genome_Size &lt;4400000.0</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -19307,31 +19353,37 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="CD8" t="b">
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC8" t="n">
         <v>0</v>
       </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>NOT_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="CF8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>Unidentified</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr"/>
-      <c r="CG8" t="inlineStr">
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>N50 &lt;20000.0; Genome_Size &lt;4400000.0</t>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
     </row>
@@ -19552,7 +19604,7 @@
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="BB9" t="n">
@@ -19641,17 +19693,17 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>GC_Content &lt;50.25; Genome_Size &gt;5700000.0</t>
+          <t>GC_Content &lt;50.09; Genome_Size &gt;5700000.0</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -19661,35 +19713,41 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="CD9" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC9" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="CF9" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>GC_Content &lt;50.25; Genome_Size &gt;5700000.0</t>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>GC_Content &lt;50.09; Genome_Size &gt;5700000.0</t>
         </is>
       </c>
     </row>
@@ -19910,7 +19968,7 @@
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="BB10" t="n">
@@ -19999,17 +20057,17 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>GC_Content &gt;50.88</t>
+          <t>GC_Content &gt;51.13; Total_Coding_Sequences &lt;4200.0</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -20019,35 +20077,41 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="CD10" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="CF10" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
-        <is>
-          <t>GC_Content &gt;50.88</t>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>GC_Content &gt;51.13; Total_Coding_Sequences &lt;4200.0</t>
         </is>
       </c>
     </row>
@@ -20367,7 +20431,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>N50 &lt;20000.0; no_of_contigs &gt;670.0</t>
+          <t>N50 &lt;20000.0; no_of_contigs &gt;670.0; Contamination &gt;2.0</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -20377,35 +20441,41 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="CD11" t="b">
-        <v>1</v>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CF11" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>N50 &lt;20000.0; no_of_contigs &gt;670.0</t>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>N50 &lt;20000.0; no_of_contigs &gt;670.0; Contamination &gt;2.0</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20785,7 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -20725,7 +20795,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Completeness_Specific &lt;100.0</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -20735,35 +20805,41 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD12" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="CF12" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
-        <is>
-          <t>none</t>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>Completeness_Specific &lt;100.0</t>
         </is>
       </c>
     </row>
@@ -21073,17 +21149,17 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>WARN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>GC_Content &lt;50.25; Genome_Size &gt;5700000.0; Total_Coding_Sequences &gt;5800.0</t>
+          <t>GC_Content &lt;50.09; Contamination &gt;2.0; Genome_Size &gt;5700000.0; Total_Coding_Sequences &gt;5800.0</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -21093,35 +21169,41 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>WARN</t>
-        </is>
-      </c>
-      <c r="CD13" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="CF13" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG13" t="inlineStr">
+      <c r="CI13" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
-        <is>
-          <t>GC_Content &lt;50.25; Genome_Size &gt;5700000.0; Total_Coding_Sequences &gt;5800.0</t>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>GC_Content &lt;50.09; Contamination &gt;2.0; Genome_Size &gt;5700000.0; Total_Coding_Sequences &gt;5800.0</t>
         </is>
       </c>
     </row>
@@ -21451,33 +21533,39 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD14" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF14" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG14" t="inlineStr">
+      <c r="CI14" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH14" t="inlineStr">
+      <c r="CJ14" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -21809,33 +21897,39 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD15" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF15" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG15" t="inlineStr">
+      <c r="CI15" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH15" t="inlineStr">
+      <c r="CJ15" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -22167,33 +22261,39 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD16" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC16" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF16" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG16" t="inlineStr">
+      <c r="CI16" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH16" t="inlineStr">
+      <c r="CJ16" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -22525,33 +22625,39 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD17" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC17" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF17" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG17" t="inlineStr">
+      <c r="CI17" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH17" t="inlineStr">
+      <c r="CJ17" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -22883,33 +22989,39 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD18" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC18" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF18" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG18" t="inlineStr">
+      <c r="CI18" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH18" t="inlineStr">
+      <c r="CJ18" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -23241,33 +23353,39 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD19" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC19" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>0</v>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF19" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG19" t="inlineStr">
+      <c r="CI19" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH19" t="inlineStr">
+      <c r="CJ19" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -23599,33 +23717,39 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD20" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC20" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0</v>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF20" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG20" t="inlineStr">
+      <c r="CI20" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH20" t="inlineStr">
+      <c r="CJ20" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -23957,33 +24081,39 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD21" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0</v>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF21" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG21" t="inlineStr">
+      <c r="CI21" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH21" t="inlineStr">
+      <c r="CJ21" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -24315,33 +24445,39 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD22" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>0</v>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF22" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG22" t="inlineStr">
+      <c r="CI22" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH22" t="inlineStr">
+      <c r="CJ22" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -24673,33 +24809,39 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD23" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD23" t="n">
+        <v>0</v>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF23" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG23" t="inlineStr">
+      <c r="CI23" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH23" t="inlineStr">
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -25031,33 +25173,39 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD24" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD24" t="n">
+        <v>0</v>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF24" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF24" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG24" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH24" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG24" t="inlineStr">
+      <c r="CI24" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH24" t="inlineStr">
+      <c r="CJ24" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -25389,33 +25537,39 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD25" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC25" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>0</v>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF25" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF25" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG25" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH25" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG25" t="inlineStr">
+      <c r="CI25" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH25" t="inlineStr">
+      <c r="CJ25" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -25747,33 +25901,39 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD26" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC26" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD26" t="n">
+        <v>0</v>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF26" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF26" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG26" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH26" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG26" t="inlineStr">
+      <c r="CI26" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH26" t="inlineStr">
+      <c r="CJ26" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -26105,33 +26265,39 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD27" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC27" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>0</v>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF27" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF27" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG27" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH27" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG27" t="inlineStr">
+      <c r="CI27" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH27" t="inlineStr">
+      <c r="CJ27" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -26463,33 +26629,39 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD28" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC28" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD28" t="n">
+        <v>0</v>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF28" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF28" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG28" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH28" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG28" t="inlineStr">
+      <c r="CI28" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH28" t="inlineStr">
+      <c r="CJ28" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -26821,33 +26993,39 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD29" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC29" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD29" t="n">
+        <v>0</v>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF29" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF29" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG29" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH29" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG29" t="inlineStr">
+      <c r="CI29" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH29" t="inlineStr">
+      <c r="CJ29" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -27179,33 +27357,39 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD30" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC30" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD30" t="n">
+        <v>0</v>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF30" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF30" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG30" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH30" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG30" t="inlineStr">
+      <c r="CI30" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH30" t="inlineStr">
+      <c r="CJ30" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -27537,33 +27721,39 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD31" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC31" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD31" t="n">
+        <v>0</v>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF31" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF31" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG31" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH31" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG31" t="inlineStr">
+      <c r="CI31" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH31" t="inlineStr">
+      <c r="CJ31" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -27895,33 +28085,39 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD32" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC32" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD32" t="n">
+        <v>0</v>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF32" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF32" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG32" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH32" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG32" t="inlineStr">
+      <c r="CI32" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH32" t="inlineStr">
+      <c r="CJ32" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -28253,33 +28449,39 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC33" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD33" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC33" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF33" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF33" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG33" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH33" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG33" t="inlineStr">
+      <c r="CI33" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH33" t="inlineStr">
+      <c r="CJ33" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -28611,33 +28813,39 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD34" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC34" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD34" t="n">
+        <v>0</v>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF34" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF34" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG34" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH34" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG34" t="inlineStr">
+      <c r="CI34" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH34" t="inlineStr">
+      <c r="CJ34" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -28969,33 +29177,39 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC35" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD35" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC35" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD35" t="n">
+        <v>0</v>
       </c>
       <c r="CE35" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF35" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF35" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG35" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH35" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG35" t="inlineStr">
+      <c r="CI35" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH35" t="inlineStr">
+      <c r="CJ35" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -29327,33 +29541,39 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC36" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD36" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC36" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD36" t="n">
+        <v>0</v>
       </c>
       <c r="CE36" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF36" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF36" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG36" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH36" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG36" t="inlineStr">
+      <c r="CI36" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH36" t="inlineStr">
+      <c r="CJ36" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -29685,33 +29905,39 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD37" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC37" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>0</v>
       </c>
       <c r="CE37" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF37" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF37" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG37" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH37" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG37" t="inlineStr">
+      <c r="CI37" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH37" t="inlineStr">
+      <c r="CJ37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -30043,33 +30269,39 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC38" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD38" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC38" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD38" t="n">
+        <v>0</v>
       </c>
       <c r="CE38" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF38" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF38" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG38" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH38" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG38" t="inlineStr">
+      <c r="CI38" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH38" t="inlineStr">
+      <c r="CJ38" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -30401,33 +30633,39 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC39" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD39" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC39" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD39" t="n">
+        <v>0</v>
       </c>
       <c r="CE39" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF39" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF39" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG39" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH39" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG39" t="inlineStr">
+      <c r="CI39" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH39" t="inlineStr">
+      <c r="CJ39" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -30759,33 +30997,39 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD40" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC40" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD40" t="n">
+        <v>0</v>
       </c>
       <c r="CE40" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF40" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF40" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG40" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH40" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG40" t="inlineStr">
+      <c r="CI40" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH40" t="inlineStr">
+      <c r="CJ40" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -31117,33 +31361,39 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC41" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD41" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC41" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD41" t="n">
+        <v>0</v>
       </c>
       <c r="CE41" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF41" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF41" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG41" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH41" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG41" t="inlineStr">
+      <c r="CI41" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH41" t="inlineStr">
+      <c r="CJ41" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -31475,33 +31725,39 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC42" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD42" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC42" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD42" t="n">
+        <v>0</v>
       </c>
       <c r="CE42" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF42" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF42" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG42" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH42" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG42" t="inlineStr">
+      <c r="CI42" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH42" t="inlineStr">
+      <c r="CJ42" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -31833,33 +32089,39 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC43" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD43" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC43" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD43" t="n">
+        <v>0</v>
       </c>
       <c r="CE43" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF43" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF43" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG43" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH43" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG43" t="inlineStr">
+      <c r="CI43" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH43" t="inlineStr">
+      <c r="CJ43" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -32191,33 +32453,39 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC44" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD44" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC44" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD44" t="n">
+        <v>0</v>
       </c>
       <c r="CE44" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF44" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF44" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG44" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH44" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG44" t="inlineStr">
+      <c r="CI44" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH44" t="inlineStr">
+      <c r="CJ44" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -32549,33 +32817,39 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC45" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD45" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC45" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD45" t="n">
+        <v>0</v>
       </c>
       <c r="CE45" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF45" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF45" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG45" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH45" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG45" t="inlineStr">
+      <c r="CI45" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH45" t="inlineStr">
+      <c r="CJ45" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -32907,33 +33181,39 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC46" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD46" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC46" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD46" t="n">
+        <v>0</v>
       </c>
       <c r="CE46" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF46" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF46" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG46" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH46" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG46" t="inlineStr">
+      <c r="CI46" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH46" t="inlineStr">
+      <c r="CJ46" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -33265,33 +33545,39 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC47" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD47" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC47" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD47" t="n">
+        <v>0</v>
       </c>
       <c r="CE47" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF47" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF47" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG47" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH47" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG47" t="inlineStr">
+      <c r="CI47" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH47" t="inlineStr">
+      <c r="CJ47" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -33623,33 +33909,39 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC48" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD48" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC48" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD48" t="n">
+        <v>0</v>
       </c>
       <c r="CE48" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF48" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF48" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG48" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH48" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG48" t="inlineStr">
+      <c r="CI48" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH48" t="inlineStr">
+      <c r="CJ48" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -33981,33 +34273,39 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC49" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD49" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC49" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD49" t="n">
+        <v>0</v>
       </c>
       <c r="CE49" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF49" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF49" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG49" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH49" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG49" t="inlineStr">
+      <c r="CI49" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH49" t="inlineStr">
+      <c r="CJ49" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -34339,33 +34637,39 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC50" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD50" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC50" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD50" t="n">
+        <v>0</v>
       </c>
       <c r="CE50" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF50" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF50" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG50" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH50" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG50" t="inlineStr">
+      <c r="CI50" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH50" t="inlineStr">
+      <c r="CJ50" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -34697,33 +35001,39 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC51" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD51" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC51" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD51" t="n">
+        <v>0</v>
       </c>
       <c r="CE51" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF51" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF51" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG51" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH51" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG51" t="inlineStr">
+      <c r="CI51" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH51" t="inlineStr">
+      <c r="CJ51" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -35055,33 +35365,39 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC52" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD52" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC52" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD52" t="n">
+        <v>0</v>
       </c>
       <c r="CE52" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF52" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF52" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG52" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH52" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG52" t="inlineStr">
+      <c r="CI52" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH52" t="inlineStr">
+      <c r="CJ52" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -35413,33 +35729,39 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC53" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD53" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC53" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
       </c>
       <c r="CE53" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF53" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF53" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG53" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH53" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG53" t="inlineStr">
+      <c r="CI53" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH53" t="inlineStr">
+      <c r="CJ53" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -35771,33 +36093,39 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC54" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD54" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC54" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD54" t="n">
+        <v>0</v>
       </c>
       <c r="CE54" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF54" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF54" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG54" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH54" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG54" t="inlineStr">
+      <c r="CI54" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH54" t="inlineStr">
+      <c r="CJ54" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -36129,33 +36457,39 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC55" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD55" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC55" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD55" t="n">
+        <v>0</v>
       </c>
       <c r="CE55" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF55" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF55" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG55" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH55" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG55" t="inlineStr">
+      <c r="CI55" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH55" t="inlineStr">
+      <c r="CJ55" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -36487,33 +36821,39 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC56" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD56" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC56" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD56" t="n">
+        <v>0</v>
       </c>
       <c r="CE56" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF56" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF56" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG56" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH56" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG56" t="inlineStr">
+      <c r="CI56" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH56" t="inlineStr">
+      <c r="CJ56" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -36845,33 +37185,39 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC57" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD57" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC57" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD57" t="n">
+        <v>0</v>
       </c>
       <c r="CE57" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF57" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF57" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG57" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH57" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG57" t="inlineStr">
+      <c r="CI57" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH57" t="inlineStr">
+      <c r="CJ57" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -37203,33 +37549,39 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC58" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD58" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC58" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD58" t="n">
+        <v>0</v>
       </c>
       <c r="CE58" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF58" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF58" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG58" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH58" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG58" t="inlineStr">
+      <c r="CI58" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH58" t="inlineStr">
+      <c r="CJ58" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -37561,33 +37913,39 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC59" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD59" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC59" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD59" t="n">
+        <v>0</v>
       </c>
       <c r="CE59" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF59" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF59" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG59" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH59" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG59" t="inlineStr">
+      <c r="CI59" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH59" t="inlineStr">
+      <c r="CJ59" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -37919,33 +38277,39 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC60" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD60" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC60" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD60" t="n">
+        <v>0</v>
       </c>
       <c r="CE60" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF60" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF60" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG60" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH60" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG60" t="inlineStr">
+      <c r="CI60" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH60" t="inlineStr">
+      <c r="CJ60" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -38277,33 +38641,39 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC61" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD61" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC61" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD61" t="n">
+        <v>0</v>
       </c>
       <c r="CE61" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF61" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF61" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG61" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH61" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG61" t="inlineStr">
+      <c r="CI61" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH61" t="inlineStr">
+      <c r="CJ61" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -38635,33 +39005,39 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC62" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD62" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC62" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD62" t="n">
+        <v>0</v>
       </c>
       <c r="CE62" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF62" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF62" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG62" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH62" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG62" t="inlineStr">
+      <c r="CI62" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH62" t="inlineStr">
+      <c r="CJ62" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -38993,33 +39369,39 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC63" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD63" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC63" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD63" t="n">
+        <v>0</v>
       </c>
       <c r="CE63" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF63" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF63" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG63" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH63" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG63" t="inlineStr">
+      <c r="CI63" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH63" t="inlineStr">
+      <c r="CJ63" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -39351,33 +39733,39 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC64" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD64" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC64" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD64" t="n">
+        <v>0</v>
       </c>
       <c r="CE64" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF64" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF64" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG64" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH64" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG64" t="inlineStr">
+      <c r="CI64" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH64" t="inlineStr">
+      <c r="CJ64" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -39709,33 +40097,39 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC65" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD65" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC65" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD65" t="n">
+        <v>0</v>
       </c>
       <c r="CE65" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF65" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF65" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG65" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH65" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG65" t="inlineStr">
+      <c r="CI65" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH65" t="inlineStr">
+      <c r="CJ65" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -40047,17 +40441,17 @@
       </c>
       <c r="BX66" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BY66" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BZ66" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="CA66" t="inlineStr">
@@ -40067,35 +40461,41 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC66" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD66" t="b">
-        <v>1</v>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD66" t="n">
+        <v>0</v>
       </c>
       <c r="CE66" t="inlineStr">
         <is>
+          <t>NOT_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="CF66" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG66" t="inlineStr">
+        <is>
           <t>Shigella flexneri</t>
         </is>
       </c>
-      <c r="CF66" t="inlineStr">
+      <c r="CH66" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG66" t="inlineStr">
+      <c r="CI66" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH66" t="inlineStr">
-        <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+      <c r="CJ66" t="inlineStr">
+        <is>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
     </row>
@@ -40405,17 +40805,17 @@
       </c>
       <c r="BX67" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BY67" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BZ67" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="CA67" t="inlineStr">
@@ -40425,35 +40825,41 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC67" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD67" t="b">
-        <v>1</v>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD67" t="n">
+        <v>0</v>
       </c>
       <c r="CE67" t="inlineStr">
         <is>
+          <t>NOT_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="CF67" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG67" t="inlineStr">
+        <is>
           <t>Shigella sonnei</t>
         </is>
       </c>
-      <c r="CF67" t="inlineStr">
+      <c r="CH67" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG67" t="inlineStr">
+      <c r="CI67" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH67" t="inlineStr">
-        <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+      <c r="CJ67" t="inlineStr">
+        <is>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
     </row>
@@ -40763,17 +41169,17 @@
       </c>
       <c r="BX68" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BY68" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BZ68" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="CA68" t="inlineStr">
@@ -40783,35 +41189,41 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC68" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD68" t="b">
-        <v>1</v>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD68" t="n">
+        <v>0</v>
       </c>
       <c r="CE68" t="inlineStr">
         <is>
+          <t>NOT_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="CF68" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG68" t="inlineStr">
+        <is>
           <t>Shigella flexneri</t>
         </is>
       </c>
-      <c r="CF68" t="inlineStr">
+      <c r="CH68" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG68" t="inlineStr">
+      <c r="CI68" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH68" t="inlineStr">
-        <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+      <c r="CJ68" t="inlineStr">
+        <is>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
     </row>
@@ -41141,33 +41553,39 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC69" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD69" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC69" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0</v>
       </c>
       <c r="CE69" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF69" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF69" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG69" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH69" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG69" t="inlineStr">
+      <c r="CI69" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH69" t="inlineStr">
+      <c r="CJ69" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -41499,33 +41917,39 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC70" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD70" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC70" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD70" t="n">
+        <v>0</v>
       </c>
       <c r="CE70" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF70" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF70" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG70" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH70" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG70" t="inlineStr">
+      <c r="CI70" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH70" t="inlineStr">
+      <c r="CJ70" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -41857,33 +42281,39 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC71" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD71" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC71" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD71" t="n">
+        <v>0</v>
       </c>
       <c r="CE71" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF71" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF71" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG71" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH71" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG71" t="inlineStr">
+      <c r="CI71" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH71" t="inlineStr">
+      <c r="CJ71" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -42215,33 +42645,39 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC72" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD72" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC72" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD72" t="n">
+        <v>0</v>
       </c>
       <c r="CE72" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF72" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF72" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG72" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH72" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG72" t="inlineStr">
+      <c r="CI72" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH72" t="inlineStr">
+      <c r="CJ72" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -42573,33 +43009,39 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC73" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD73" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC73" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD73" t="n">
+        <v>0</v>
       </c>
       <c r="CE73" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF73" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF73" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG73" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH73" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG73" t="inlineStr">
+      <c r="CI73" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH73" t="inlineStr">
+      <c r="CJ73" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -42931,33 +43373,39 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC74" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD74" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC74" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD74" t="n">
+        <v>0</v>
       </c>
       <c r="CE74" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF74" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF74" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG74" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH74" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG74" t="inlineStr">
+      <c r="CI74" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH74" t="inlineStr">
+      <c r="CJ74" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -43289,33 +43737,39 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC75" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD75" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC75" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>0</v>
       </c>
       <c r="CE75" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF75" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF75" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG75" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH75" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG75" t="inlineStr">
+      <c r="CI75" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH75" t="inlineStr">
+      <c r="CJ75" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -43647,33 +44101,39 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC76" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD76" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC76" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0</v>
       </c>
       <c r="CE76" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF76" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF76" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG76" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH76" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG76" t="inlineStr">
+      <c r="CI76" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH76" t="inlineStr">
+      <c r="CJ76" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -44005,33 +44465,39 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC77" t="inlineStr">
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC77" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE77" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="CD77" t="b">
-        <v>1</v>
-      </c>
-      <c r="CE77" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF77" t="inlineStr">
+      <c r="CF77" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG77" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH77" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG77" t="inlineStr">
+      <c r="CI77" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH77" t="inlineStr">
+      <c r="CJ77" t="inlineStr">
         <is>
           <t>GC_Content &lt;50.25</t>
         </is>
@@ -44363,33 +44829,39 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC78" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD78" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC78" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>0</v>
       </c>
       <c r="CE78" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF78" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF78" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG78" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH78" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG78" t="inlineStr">
+      <c r="CI78" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH78" t="inlineStr">
+      <c r="CJ78" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -44721,33 +45193,39 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC79" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD79" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC79" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>0</v>
       </c>
       <c r="CE79" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF79" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF79" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG79" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH79" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG79" t="inlineStr">
+      <c r="CI79" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH79" t="inlineStr">
+      <c r="CJ79" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -45079,33 +45557,39 @@
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC80" t="inlineStr">
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC80" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="CD80" t="b">
-        <v>1</v>
-      </c>
-      <c r="CE80" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF80" t="inlineStr">
+      <c r="CF80" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG80" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH80" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG80" t="inlineStr">
+      <c r="CI80" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH80" t="inlineStr">
+      <c r="CJ80" t="inlineStr">
         <is>
           <t>GC_Content &lt;50.25</t>
         </is>
@@ -45437,33 +45921,39 @@
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC81" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD81" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>0</v>
       </c>
       <c r="CE81" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF81" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF81" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG81" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH81" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG81" t="inlineStr">
+      <c r="CI81" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH81" t="inlineStr">
+      <c r="CJ81" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -45795,33 +46285,39 @@
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC82" t="inlineStr">
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC82" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE82" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="CD82" t="b">
-        <v>1</v>
-      </c>
-      <c r="CE82" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF82" t="inlineStr">
+      <c r="CF82" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG82" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH82" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG82" t="inlineStr">
+      <c r="CI82" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH82" t="inlineStr">
+      <c r="CJ82" t="inlineStr">
         <is>
           <t>GC_Content &lt;50.25</t>
         </is>
@@ -46153,33 +46649,39 @@
       </c>
       <c r="CB83" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC83" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD83" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC83" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD83" t="n">
+        <v>0</v>
       </c>
       <c r="CE83" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF83" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF83" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG83" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH83" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG83" t="inlineStr">
+      <c r="CI83" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH83" t="inlineStr">
+      <c r="CJ83" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -46511,33 +47013,39 @@
       </c>
       <c r="CB84" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC84" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD84" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC84" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD84" t="n">
+        <v>0</v>
       </c>
       <c r="CE84" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF84" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF84" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG84" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH84" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG84" t="inlineStr">
+      <c r="CI84" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH84" t="inlineStr">
+      <c r="CJ84" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -46869,33 +47377,39 @@
       </c>
       <c r="CB85" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC85" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD85" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC85" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD85" t="n">
+        <v>0</v>
       </c>
       <c r="CE85" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF85" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF85" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG85" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH85" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG85" t="inlineStr">
+      <c r="CI85" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH85" t="inlineStr">
+      <c r="CJ85" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -47227,33 +47741,39 @@
       </c>
       <c r="CB86" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC86" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD86" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC86" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD86" t="n">
+        <v>0</v>
       </c>
       <c r="CE86" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF86" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF86" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG86" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH86" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG86" t="inlineStr">
+      <c r="CI86" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH86" t="inlineStr">
+      <c r="CJ86" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -47585,33 +48105,39 @@
       </c>
       <c r="CB87" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC87" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD87" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC87" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD87" t="n">
+        <v>0</v>
       </c>
       <c r="CE87" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF87" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF87" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG87" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH87" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG87" t="inlineStr">
+      <c r="CI87" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH87" t="inlineStr">
+      <c r="CJ87" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -47943,33 +48469,39 @@
       </c>
       <c r="CB88" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC88" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD88" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC88" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD88" t="n">
+        <v>0</v>
       </c>
       <c r="CE88" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF88" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF88" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG88" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH88" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG88" t="inlineStr">
+      <c r="CI88" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH88" t="inlineStr">
+      <c r="CJ88" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -48301,33 +48833,39 @@
       </c>
       <c r="CB89" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC89" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD89" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC89" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD89" t="n">
+        <v>0</v>
       </c>
       <c r="CE89" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF89" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF89" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG89" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH89" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG89" t="inlineStr">
+      <c r="CI89" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH89" t="inlineStr">
+      <c r="CJ89" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -48659,33 +49197,39 @@
       </c>
       <c r="CB90" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC90" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD90" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC90" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD90" t="n">
+        <v>0</v>
       </c>
       <c r="CE90" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF90" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF90" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG90" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH90" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG90" t="inlineStr">
+      <c r="CI90" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH90" t="inlineStr">
+      <c r="CJ90" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -49017,33 +49561,39 @@
       </c>
       <c r="CB91" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC91" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD91" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC91" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD91" t="n">
+        <v>0</v>
       </c>
       <c r="CE91" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF91" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF91" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG91" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH91" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG91" t="inlineStr">
+      <c r="CI91" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH91" t="inlineStr">
+      <c r="CJ91" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -49375,33 +49925,39 @@
       </c>
       <c r="CB92" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC92" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD92" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC92" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD92" t="n">
+        <v>0</v>
       </c>
       <c r="CE92" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF92" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF92" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG92" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH92" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG92" t="inlineStr">
+      <c r="CI92" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH92" t="inlineStr">
+      <c r="CJ92" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -49733,33 +50289,39 @@
       </c>
       <c r="CB93" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC93" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD93" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC93" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
       </c>
       <c r="CE93" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF93" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF93" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG93" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH93" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG93" t="inlineStr">
+      <c r="CI93" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH93" t="inlineStr">
+      <c r="CJ93" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -50091,33 +50653,39 @@
       </c>
       <c r="CB94" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC94" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD94" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC94" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD94" t="n">
+        <v>0</v>
       </c>
       <c r="CE94" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF94" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF94" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG94" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH94" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG94" t="inlineStr">
+      <c r="CI94" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH94" t="inlineStr">
+      <c r="CJ94" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -50449,33 +51017,39 @@
       </c>
       <c r="CB95" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC95" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD95" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC95" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD95" t="n">
+        <v>0</v>
       </c>
       <c r="CE95" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF95" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF95" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG95" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH95" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG95" t="inlineStr">
+      <c r="CI95" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH95" t="inlineStr">
+      <c r="CJ95" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -50807,33 +51381,39 @@
       </c>
       <c r="CB96" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC96" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD96" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC96" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD96" t="n">
+        <v>0</v>
       </c>
       <c r="CE96" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF96" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF96" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG96" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH96" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG96" t="inlineStr">
+      <c r="CI96" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH96" t="inlineStr">
+      <c r="CJ96" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -51165,33 +51745,39 @@
       </c>
       <c r="CB97" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC97" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD97" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC97" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD97" t="n">
+        <v>0</v>
       </c>
       <c r="CE97" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF97" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF97" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG97" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH97" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG97" t="inlineStr">
+      <c r="CI97" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH97" t="inlineStr">
+      <c r="CJ97" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -51503,17 +52089,17 @@
       </c>
       <c r="BX98" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BY98" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="BZ98" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
       <c r="CA98" t="inlineStr">
@@ -51523,35 +52109,41 @@
       </c>
       <c r="CB98" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC98" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD98" t="b">
-        <v>1</v>
+          <t>not available</t>
+        </is>
+      </c>
+      <c r="CC98" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD98" t="n">
+        <v>0</v>
       </c>
       <c r="CE98" t="inlineStr">
         <is>
+          <t>NOT_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="CF98" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG98" t="inlineStr">
+        <is>
           <t>Shigella dysenteriae</t>
         </is>
       </c>
-      <c r="CF98" t="inlineStr">
+      <c r="CH98" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG98" t="inlineStr">
+      <c r="CI98" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH98" t="inlineStr">
-        <is>
-          <t>Speciator.genusName; Speciator.speciesName</t>
+      <c r="CJ98" t="inlineStr">
+        <is>
+          <t>No pinned QualiBact scheme for species</t>
         </is>
       </c>
     </row>
@@ -51881,33 +52473,39 @@
       </c>
       <c r="CB99" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC99" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD99" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC99" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD99" t="n">
+        <v>0</v>
       </c>
       <c r="CE99" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF99" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF99" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG99" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH99" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG99" t="inlineStr">
+      <c r="CI99" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH99" t="inlineStr">
+      <c r="CJ99" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -52239,33 +52837,39 @@
       </c>
       <c r="CB100" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC100" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD100" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC100" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
       </c>
       <c r="CE100" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF100" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF100" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG100" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH100" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG100" t="inlineStr">
+      <c r="CI100" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH100" t="inlineStr">
+      <c r="CJ100" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -52597,33 +53201,39 @@
       </c>
       <c r="CB101" t="inlineStr">
         <is>
-          <t>QualiBact Escherichia_coli qualibact-v1.0 ATB tier logic</t>
-        </is>
-      </c>
-      <c r="CC101" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="CD101" t="b">
-        <v>1</v>
+          <t>Pinned QualiBact scheme for Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CC101" t="n">
+        <v>8</v>
+      </c>
+      <c r="CD101" t="n">
+        <v>0</v>
       </c>
       <c r="CE101" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="CF101" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="CF101" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG101" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="CH101" t="inlineStr">
         <is>
           <t>good</t>
         </is>
       </c>
-      <c r="CG101" t="inlineStr">
+      <c r="CI101" t="inlineStr">
         <is>
           <t>QualiBact Escherichia coli qualibact-v1.0</t>
         </is>
       </c>
-      <c r="CH101" t="inlineStr">
+      <c r="CJ101" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -53012,12 +53622,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -53054,12 +53664,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
     </row>
@@ -56990,7 +57600,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
